--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45188</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>45936</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46121</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>44510</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>44510</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>46106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>46121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>45566</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>46204</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>44945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>46140</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>45950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>44467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45063</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>46252</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46164</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>46211</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>45419</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>46238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44956</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>44860</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44577</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44880</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44459</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44469</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44529</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44461</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44733</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>44860</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44833</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44785</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>44522</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44508</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44816</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44733</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45117</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45295</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45712</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>44894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45712</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45147</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>44970</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44970</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45259</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45266</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45586</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45541</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45406</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45190</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45170</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45225</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45667</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45201</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45415</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44580</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45708</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45259</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45191</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45321</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45079</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44529</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45667</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45063</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45355</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45553</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45446</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45678</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45105</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45226</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45660</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45841</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45401</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45737</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45799</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45890</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45259</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45890</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45892</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45892</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45719</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>45638</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45587</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45063</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44981</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45904</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>46070</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45906</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45265</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>46003</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45708</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45993</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>46052</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45665</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45054</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45706</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45915</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>46003</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45894</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45912</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45917</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45916</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45460</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45919</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45406</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44924</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44756</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45925</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45881</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45881</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45925</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45385</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45929</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45926</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>46142</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45238</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45931</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45930</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45930</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>45691</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45641</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45932</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45933</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45936</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45936</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45936</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45936</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>46146</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45939</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>44706</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45943</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>46146</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45943</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45940</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45037</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>46148</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45943</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45740</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45945</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45945</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45246</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45946</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45946</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45582</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45950</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45950</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45950</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45950</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45457</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44950</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>44581</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>45754</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44907</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45419</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45112</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45965</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44901</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45641</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45213</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>46009</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>46003</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45971</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45299</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45730</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45314</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45308</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>46154</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>46154</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45492</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>46003</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45979</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45698</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45723</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45980</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45719</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45981</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46155</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45629</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45985</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45980</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45985</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>46154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>46154</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46081</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45985</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>44970</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45988</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>46160</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45988</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>46160</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>46161</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44520</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45175</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45993</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45204</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46163</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45602</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45995</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>44964</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45639</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>46001</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46167</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45159</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45986</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46003</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46003</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>46003</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45700</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45302</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>46003</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46003</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44970</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45632</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45622</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>46167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46009</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45420</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>46009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>46003</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>45678</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>46009</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>46013</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45204</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45917</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45272</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45771</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>46168</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45054</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44488</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>46021</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>44956</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>46021</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44903</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45698</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>46029</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45210</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>46029</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>46029</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45617</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>46030</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45561</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>46031</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>46031</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46030</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>46031</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>46035</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>46035</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>46035</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>46171</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45063</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45583</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45542</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>45282</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>46041</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>46041</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45295</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45629</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>46175</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>46175</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44894</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46175</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>46056</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45253</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>46056</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45364</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>46058</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45999</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45009</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>46178</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45553</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45660</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44522</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>46066</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45266</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45173</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46077</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45679</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44956</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45470</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45415</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45415</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>46083</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>44894</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>46085</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>46090</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44901</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45505</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46090</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46092</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46091</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>46091</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>46091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46094</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>46093</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>45054</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45054</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>46195</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>46097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>46191</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46195</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>46195</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46106</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>46106</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>46106</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45392</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45044</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>46197</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46199</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>44712</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45737</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46122</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45215</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>46128</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>46203</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45225</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45044</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46135</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>46135</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>46246</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>46134</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45481</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44974</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>44974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>46204</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46204</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45170</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45049</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>46204</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46204</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>46246</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>46246</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44992</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45510</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44964</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>44964</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46248</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>44532</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44980</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>44903</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>46252</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45266</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45266</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44862</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45700</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>46252</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>46252</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>46254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45058</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45573</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>46255</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46255</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46254</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45393</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45247</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46258</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45237</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45419</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46258</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45629</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46258</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45679</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45429</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>44603</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45145</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>46221</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45261</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45175</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44894</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45719</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46267</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45163</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45266</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45112</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>46267</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>46267</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45198</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>44722</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45054</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45035</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>45685</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>44924</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>46269</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46225</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45777</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45005</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>46272</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46274</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>46233</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46274</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>46275</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46275</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45785</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46275</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>46275</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39220,7 +39220,7 @@
         <v>46233</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45784</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45405</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45429</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>46234</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45748</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>46279</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45268</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>46279</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>44917</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46280</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46238</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45790</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>46238</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46238</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45363</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45645</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>45173</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45799</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45799</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45799</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>45799</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>45681</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>46282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46282</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45805</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45811</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45811</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45811</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45692</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45721</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45321</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>45812</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>45816</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45816</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45816</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>45816</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45815</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45815</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45816</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42336,7 +42336,7 @@
         <v>45816</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42409,7 +42409,7 @@
         <v>45816</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
         <v>45816</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42555,7 +42555,7 @@
         <v>45816</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45816</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45816</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45816</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45816</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45816</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45816</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45816</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45816</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45815</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45816</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45816</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45816</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45815</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45816</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45815</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45820</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45820</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43879,7 +43879,7 @@
         <v>45825</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43952,7 +43952,7 @@
         <v>45827</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45831</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45832</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45835</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45841</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45813</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45842</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>44776</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45842</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45842</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45851</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45866</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45867</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45859</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45841</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>44678</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45393</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45061</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>44944</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45393</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45061</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>45393</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45061</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45383</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45733</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45747</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45747</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45756</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45775</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45775</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>46162</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>46190</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>46190</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45566</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44728</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45791</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45268</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45419</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>46140</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45063</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>46170</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>44467</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46252</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46211</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44945</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>44956</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44860</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44489</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44853</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44497</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44669</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44880</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45266</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45678</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45406</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45253</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45393</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45238</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45243</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44907</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>46021</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>46021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45266</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46030</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46030</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45299</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44520</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46031</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45173</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45799</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46035</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45660</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45841</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45259</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45890</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45737</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45892</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45892</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45799</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45645</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45681</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>45799</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>46041</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>46041</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45363</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45835</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44874</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45906</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45054</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45909</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44924</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44894</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45272</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>46055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>46056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>46056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45912</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45916</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45364</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45894</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45691</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45919</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>46066</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45583</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44603</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45805</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46073</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46077</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45930</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45929</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46083</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45225</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45721</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45932</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>46085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45936</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45321</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45933</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45692</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>46090</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>46091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>46091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46091</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45938</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45698</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46093</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45708</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45940</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45939</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>46094</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>46097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45943</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45943</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45945</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45945</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45950</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45950</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45950</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45415</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>46106</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>46106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45587</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45420</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45295</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45049</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45308</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45964</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45811</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45811</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46122</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45811</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45971</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45816</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45009</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45815</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45815</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45816</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45816</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45980</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45979</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44974</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45980</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>44956</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>46134</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>46134</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45981</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45816</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45629</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45985</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45985</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45461</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45815</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45815</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45816</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45988</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45629</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45816</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46135</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45204</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>46135</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45723</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45994</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45706</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45993</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45147</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46052</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45446</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45995</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44980</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45815</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45816</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45816</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46001</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45665</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45816</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45816</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45816</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45816</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45816</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45816</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45816</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45816</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45816</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>46003</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46003</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>46003</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>46003</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45816</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45816</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46003</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45993</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>46003</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>46003</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45820</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45820</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>46003</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46070</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44756</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45708</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>46009</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>46009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46003</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>46013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46013</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45881</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45201</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46003</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45825</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45246</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45827</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44488</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45054</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45054</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45266</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45266</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45210</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46146</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45719</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45641</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45831</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>46146</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45832</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45541</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>46081</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>46154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45737</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>46154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>46009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>46154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>46154</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45986</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45063</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46155</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46003</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46003</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45204</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>44970</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46160</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45054</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>45295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45406</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45229</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45321</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45842</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45842</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44901</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45842</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45622</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44776</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>46163</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45639</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45851</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44992</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46167</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45266</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45266</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46168</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45247</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46168</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44532</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44936</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46171</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45866</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46175</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46175</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46175</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45867</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45573</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46178</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45999</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45457</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45602</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44580</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44522</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45170</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45754</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45585</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45215</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45470</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>46195</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45629</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46195</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>46195</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46197</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45191</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45719</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45719</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>46199</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45859</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46199</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45841</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46203</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44648</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45163</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44995</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46204</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45667</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45510</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46252</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45679</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45392</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46254</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>44862</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>46255</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46255</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>46258</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>46258</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45175</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46258</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45415</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45415</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44749</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45170</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45314</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>46221</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45213</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46267</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>44722</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44706</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46225</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45355</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45251</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45771</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46272</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46269</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>46274</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46233</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46275</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46275</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>46275</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>46233</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46275</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46280</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46279</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46279</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44970</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>44970</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46279</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>46234</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46238</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46282</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45282</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46238</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>46238</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>46238</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45505</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46282</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46286</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44964</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>46286</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45302</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45266</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45266</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45266</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45553</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44903</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45492</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46286</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46029</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46288</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45561</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45419</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>46286</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>46290</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45036</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46009</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46246</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46248</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>46246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>44964</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>44901</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45712</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45112</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45259</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45641</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45145</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45266</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>44956</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45730</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45679</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45159</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45401</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45226</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44894</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45105</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44898</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>45632</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>45582</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45537</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45054</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45712</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45225</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45385</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45560</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>45700</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45719</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45678</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44981</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45586</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45063</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45237</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>45173</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45460</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45058</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45542</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>44970</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45638</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45117</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45660</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45667</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45777</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45784</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45005</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45405</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45785</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44917</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45748</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45790</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45429</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45268</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>44678</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45393</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45061</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>44944</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45393</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45061</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45393</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45061</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45383</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45733</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45747</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45756</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45775</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>46162</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45566</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44728</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>45791</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>46232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45268</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45419</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>46140</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45063</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>46170</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>44467</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46252</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46211</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44945</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>44956</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45747</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>44860</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44489</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>44853</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44497</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>44669</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44880</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45266</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45678</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45406</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45253</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45393</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44894</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45238</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45243</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44907</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>46021</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>46021</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45266</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46030</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46030</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46030</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45299</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44520</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>46029</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46031</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>46031</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>46031</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45173</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45799</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>46035</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45660</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45841</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45259</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45890</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45737</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45892</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45892</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45799</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45645</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45681</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>45799</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>46041</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>46041</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45363</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45835</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44529</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44874</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45906</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45054</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45909</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44924</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44894</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45272</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>46055</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>46056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>46056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45912</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45916</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45364</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45894</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45691</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45919</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>46066</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44581</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45583</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44603</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45805</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46073</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46077</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45930</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45929</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>46083</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45225</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45721</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45932</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>46085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45936</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45321</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45933</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>45692</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>46090</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>46091</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>46091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46091</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45938</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45698</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46093</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45708</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45940</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45939</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>46094</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>46097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45943</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45943</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45259</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45945</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45945</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45945</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45945</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45945</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45950</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45950</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45950</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46106</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45952</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45415</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>46106</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>46106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45587</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45420</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45295</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45049</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45308</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45964</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45811</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45811</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46122</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45811</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45971</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45816</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45009</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45815</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45815</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45816</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45816</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45980</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45979</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44974</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45980</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>44956</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>46134</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>46134</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45981</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45816</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45629</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45985</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45985</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45461</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45815</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45815</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45816</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45988</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45988</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45629</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45816</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>46135</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45204</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>46135</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45723</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45994</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45706</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45993</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45147</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46052</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>44712</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45446</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45995</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44980</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45815</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45816</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45816</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46001</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45665</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45816</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45816</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45816</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45816</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45816</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45816</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45816</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45816</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45816</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45816</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>46003</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46003</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>46003</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>46003</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45816</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45816</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46003</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45993</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>46003</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>46003</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45820</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45820</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>46003</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46070</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44756</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45708</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>46009</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>46009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46003</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>46013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46013</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45881</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45063</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45201</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45881</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46003</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45825</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45246</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45827</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44488</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45054</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45054</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45266</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45266</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>44733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45210</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46146</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45719</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45641</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45831</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>46146</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45832</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45541</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>46081</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>46154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45737</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>46154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>46009</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>46154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>46154</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45986</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45063</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46155</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46003</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46003</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45204</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>44970</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46160</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45054</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>45295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45406</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45229</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45321</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45842</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45842</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44901</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45842</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45622</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44776</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>46163</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45986</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45639</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45813</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45851</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44992</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46167</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45266</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45266</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>46168</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45247</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46168</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45198</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>44532</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44936</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46171</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45866</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>46175</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46175</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46175</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45867</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45573</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>46178</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>45999</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45457</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45602</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44580</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44522</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45170</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>46191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45754</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45585</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45215</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45470</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>46195</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45629</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>46195</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>46195</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46197</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45191</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45719</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>45719</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>46199</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45859</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46199</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45841</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46203</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44648</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45163</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44995</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46204</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45667</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45510</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46252</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45679</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45392</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46254</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46254</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>44862</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>46255</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46255</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>46258</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>46258</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45175</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46258</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45415</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45415</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44749</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45170</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45314</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>46221</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45213</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46267</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>44722</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44706</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46225</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>46267</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45355</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45251</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45771</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>46272</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>46269</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>46274</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46233</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46275</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46275</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>46275</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>46233</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46275</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46280</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46279</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>46279</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44970</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>44970</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46279</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>46234</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46238</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46282</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45282</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46238</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>46238</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>46238</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45505</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>46282</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46286</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44964</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>46286</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45302</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45266</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45266</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45266</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45553</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44903</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45492</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46286</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46029</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46288</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45561</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45419</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>46286</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>46246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>46290</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45036</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>46009</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>46246</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46248</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>46289</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>46246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>44964</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>44901</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45712</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45112</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45259</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45641</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45145</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45266</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>44956</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45730</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45679</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45159</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45401</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45226</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44894</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45105</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44898</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>45632</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>45582</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45537</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45054</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45712</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45225</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45385</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45560</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>45700</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>45719</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45678</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44981</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45586</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45063</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45237</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>45173</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45460</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45058</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45542</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>44970</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45638</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45117</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45660</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45667</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45777</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45784</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45005</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45405</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45785</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>44917</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45748</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45790</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45429</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45268</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>44678</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45393</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45061</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>44944</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45393</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45061</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45393</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45061</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45383</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45733</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45747</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45756</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45775</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>46162</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45566</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46204</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46140</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46170</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46164</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45063</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46252</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45419</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44956</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44489</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>44577</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44669</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44720</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>44776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44785</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44733</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44833</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44721</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45229</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45537</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44648</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45585</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44512</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45268</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>45295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44917</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>46003</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45712</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46003</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>46003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46003</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46003</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>46009</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46009</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>46003</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>46013</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>46013</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>44894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45660</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>46021</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>45841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45737</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45890</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>45259</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44970</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45892</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45892</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>46029</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45617</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45629</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>46030</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>46030</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46031</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45835</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>46031</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>46035</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>46041</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46041</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45906</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45909</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45586</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45406</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45912</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45363</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45173</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45799</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45916</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45799</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45681</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45170</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46055</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44924</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45811</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45925</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>46056</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45190</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>46056</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45929</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45926</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45364</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45719</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45931</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45667</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45201</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45933</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45811</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45938</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>46073</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45943</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45692</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45940</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45721</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45945</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45415</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46077</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45946</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44580</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45952</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45952</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45246</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>46083</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>46085</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45816</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>46090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45816</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45816</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>46091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>46091</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>46091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45815</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45815</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45816</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45816</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45816</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45816</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45816</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45816</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45816</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45816</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45816</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45816</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45816</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45816</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46094</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45259</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45815</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45816</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45191</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45967</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45971</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45461</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>46097</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45321</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44529</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45063</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>46104</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45815</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>45816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45815</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45667</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>45979</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45816</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45079</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45980</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45981</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45355</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45985</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45820</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45820</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45988</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45993</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45993</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45994</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45995</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45827</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46128</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45831</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45226</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45832</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45401</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46135</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>46135</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46134</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45835</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45719</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45638</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45587</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44981</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45842</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45446</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44776</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45842</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45265</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45266</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45054</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45851</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45460</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45406</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45385</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45238</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45243</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>46070</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45691</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>46003</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45708</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45993</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>46052</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45665</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45867</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>46003</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44706</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44903</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45740</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44756</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45881</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45582</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46142</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45641</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45457</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44950</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44581</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45754</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44907</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>44903</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46146</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45419</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44901</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46009</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>46003</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>46154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46003</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45641</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46155</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45985</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>46154</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>46081</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44970</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45730</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45204</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45314</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>46163</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45308</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45492</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45560</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45112</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>44749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45723</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45639</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45719</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45719</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>46167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45629</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>44898</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45700</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45622</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46167</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45859</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46168</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>46171</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44520</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46175</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46175</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46175</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45602</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>44964</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45159</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45302</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45632</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46195</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45420</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45678</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>46195</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45771</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46195</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45054</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44488</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>46197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44956</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46199</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>44903</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45210</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>46203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45561</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45063</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45583</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45510</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45542</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45282</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45295</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45629</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46258</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>46258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>44894</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46221</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45253</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45553</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45660</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>44522</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46267</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>46267</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>46267</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>45266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>46269</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>46225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45173</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45679</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>44956</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45470</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45415</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45415</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>46274</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>46233</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44894</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46274</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46275</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46233</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46234</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>46238</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44901</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45505</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>46238</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>46238</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45054</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45054</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46282</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>46282</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46029</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46286</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45392</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46286</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46286</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45044</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46289</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>46246</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44712</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46289</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45737</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>46246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46248</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46009</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>45215</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46290</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45225</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45044</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46290</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>45481</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44974</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44974</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>46294</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46252</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45930</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45049</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46058</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45005</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46296</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46254</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44992</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46255</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>44964</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46254</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>46254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44964</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46092</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>44532</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44980</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>44903</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>45266</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>45266</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44862</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45700</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45058</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45573</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45393</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44995</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45237</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45419</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45629</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45679</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45429</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>44603</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45145</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45261</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45175</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>44894</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45719</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45163</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45266</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45266</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45112</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>44722</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45054</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45035</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45685</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>44924</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45777</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45785</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45784</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45405</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45429</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45748</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45393</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45061</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>44944</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45393</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45061</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45393</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45061</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45383</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45733</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45756</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46162</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>45566</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46204</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>46036</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>46036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46140</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>46170</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>46164</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>46211</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45063</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46252</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45419</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44956</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44489</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>44577</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44669</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44720</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>44776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44785</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44733</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44833</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44721</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45229</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45537</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44648</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45585</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44874</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44733</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44512</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45268</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>45295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>44917</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>46003</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45712</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46003</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>46003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46003</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46003</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>46009</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46009</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>46003</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>46009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>46013</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>46013</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>44894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45660</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>46021</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>45841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45737</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45890</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>45259</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44970</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45892</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45892</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>46029</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45617</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45629</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>46030</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>46030</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45266</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46031</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45835</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>46030</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>46031</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>46035</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>46041</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>46041</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45906</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45909</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45586</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45541</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45406</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>45912</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45363</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45173</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45799</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45916</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45799</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45681</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45170</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46055</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44924</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45811</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45925</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>46056</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45190</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>46056</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45929</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45929</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45926</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45364</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45719</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45931</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45667</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45201</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45933</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46066</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45811</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45938</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>46073</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45943</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45943</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45692</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45940</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45721</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45945</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45415</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46077</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45931</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45946</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45946</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>45950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45950</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44580</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>45952</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45952</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45246</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>46083</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45708</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>46085</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45816</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>46090</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45816</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45816</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>46091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>46091</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>46091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45815</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45815</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45816</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45816</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45816</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45816</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45816</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45816</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45816</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45816</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45816</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45816</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45816</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45816</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46094</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45259</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45815</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45816</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45816</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45191</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         <v>45816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45967</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>45971</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45461</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>46097</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         <v>45321</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44529</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45063</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>46104</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45815</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>45816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45815</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>45667</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>45979</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46106</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46106</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45816</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45079</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45980</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45981</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45981</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45355</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45985</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45820</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45820</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45988</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46122</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45993</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45993</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45994</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45995</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45827</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46128</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45831</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45105</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45226</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45832</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45401</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46135</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>46135</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46134</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46134</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45835</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45719</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45638</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45587</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44981</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45842</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45446</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>44776</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45842</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45265</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45266</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45054</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45851</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45460</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45406</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45385</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45238</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45243</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>46070</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45691</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>46003</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45708</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45993</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>46052</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45665</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45867</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>46003</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44706</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44903</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45740</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44756</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45881</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45582</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46142</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45641</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45457</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44950</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>44581</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45754</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44907</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>44903</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46146</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45419</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44901</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>46009</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>46003</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46154</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>46154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>46003</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45641</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46155</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45985</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>46154</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>46081</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44970</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45730</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46160</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>46161</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45204</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45314</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>46163</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45308</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45492</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45560</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45112</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>44749</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45723</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>45639</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45719</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45719</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>46167</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45629</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>44898</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45700</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45622</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46167</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45859</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46168</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>46171</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44520</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46175</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46175</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46175</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45602</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>44964</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45159</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45302</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45632</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46195</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45420</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45678</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45204</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>46195</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45272</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45771</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46195</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45054</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44488</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>46197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44956</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46199</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>44903</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45698</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45210</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>46203</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45561</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45063</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45583</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45510</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45542</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45282</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45295</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45629</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46258</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>46258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>44894</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46221</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45253</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45553</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45660</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>44522</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46267</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>46267</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>46267</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>45266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>46269</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>46225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45173</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45679</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>44956</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>45470</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45415</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45415</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>46274</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>46233</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44894</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46274</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46275</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46275</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46233</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46234</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>46238</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>44901</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>46238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45505</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>46238</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>46238</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45054</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45054</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46282</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>46282</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46029</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46286</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45392</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46286</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46286</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45044</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46289</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>46246</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44712</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46289</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45737</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>46246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46248</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46009</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>45215</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46290</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45225</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45044</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40580,7 +40580,7 @@
         <v>46290</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40653,7 +40653,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>45481</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44974</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44974</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>46252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         <v>46294</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45170</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46252</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45930</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45049</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46058</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45005</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46296</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46254</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44992</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46255</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46255</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>44964</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46254</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         <v>46254</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>44964</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46092</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>44532</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44980</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>44903</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>45266</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>45266</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>44862</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45700</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45058</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45573</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45393</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45247</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44995</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45237</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45419</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45629</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45679</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45429</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>44603</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45145</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45261</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45175</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>44894</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45719</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45163</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45266</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45266</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45112</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>44722</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45054</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45035</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45685</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>44924</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45777</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45785</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45784</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45405</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45429</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>45748</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45393</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45061</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>44944</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45393</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45061</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45393</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45061</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45383</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45733</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45756</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46162</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45566</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46204</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45419</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44945</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46140</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46170</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>46211</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46164</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44956</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44489</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>44577</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44669</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44720</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>44776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44874</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44721</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44785</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45541</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45406</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44956</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45730</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45679</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45159</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44816</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45737</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45265</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45063</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45105</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45406</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45632</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44529</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45321</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44901</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45678</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45054</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45225</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44992</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45560</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45238</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45266</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45243</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45719</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44907</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45586</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45237</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45173</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45460</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45247</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45266</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45058</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45419</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45542</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45299</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45660</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45890</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45841</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45259</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45890</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45737</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44520</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45892</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45892</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>44964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45117</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45660</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45481</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45906</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45667</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45909</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44529</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45912</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45457</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44874</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45915</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45784</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45054</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>44894</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45917</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45785</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>44903</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44917</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44522</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45748</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45691</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45919</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45790</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45754</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45429</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45268</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45583</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45925</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45925</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45926</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>44894</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45215</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45037</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44603</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45470</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45930</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45930</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45553</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45719</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45719</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45929</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45932</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45225</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45932</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44648</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45173</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45163</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45799</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44995</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45645</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45681</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45799</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45363</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45698</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45933</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45936</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45708</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45667</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45805</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45429</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45721</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45692</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45679</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45940</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45939</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45415</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45943</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45943</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45943</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45943</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45587</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45946</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45811</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45811</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45945</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45945</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45946</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45420</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>45945</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45816</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45392</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45295</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45815</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45815</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45816</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45816</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44862</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45816</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>45815</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45815</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45816</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45816</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45816</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45950</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45815</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45816</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45816</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45950</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45816</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45816</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45816</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45816</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45816</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45816</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45816</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45816</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45816</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45816</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45820</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45825</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45175</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45952</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45951</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45952</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45415</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45415</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45964</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44512</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45965</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44956</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45967</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45035</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45842</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45842</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45629</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45842</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45461</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44776</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45170</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45629</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45813</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45314</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45719</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45213</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45723</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45147</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>44712</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>44722</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45816</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>44706</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45866</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45355</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45251</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45771</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45867</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45979</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45980</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45044</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45859</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45201</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45044</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45685</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46097</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45246</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44970</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45282</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45505</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44488</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45054</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>45054</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45988</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44733</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45210</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45719</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45266</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45266</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45266</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45994</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45553</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>44903</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46122</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>45492</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45995</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46128</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45561</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45419</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46003</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46003</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46003</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>46134</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46134</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>46003</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>46003</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46003</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>46003</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>46135</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>46135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>46009</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>46009</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>46009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>46003</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>45706</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>44964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>46052</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45917</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46021</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45446</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>46021</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44901</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45617</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46030</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45665</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46030</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46029</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46029</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46031</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46031</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45712</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>46035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>46003</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46035</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44756</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45708</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46035</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45112</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46041</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46041</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45881</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45641</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45145</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46003</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45266</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45246</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45175</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46055</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46056</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>46056</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45364</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>46142</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45641</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>46081</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46154</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45985</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46073</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46077</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>46154</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>46083</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>46009</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45986</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46003</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>46003</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>46090</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>46090</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45204</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>46091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>44970</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>46091</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>46160</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>46091</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46093</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>46160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>46094</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45622</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46163</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45700</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45986</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45639</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46167</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46168</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>46168</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>46175</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46175</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>46178</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46191</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46195</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>46197</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>46204</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>46204</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45510</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>46221</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46267</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46267</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46267</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46225</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>46272</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46269</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46274</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46274</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46233</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46275</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>46233</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46275</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>46280</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46279</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>46234</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46282</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46238</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>46238</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46286</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46286</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46286</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>46029</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>46288</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46288</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46286</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46290</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46009</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46246</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46289</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46246</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46289</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>46290</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>46252</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>46294</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46248</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46252</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46246</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>46252</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46252</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45005</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46296</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46254</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46254</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46255</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>46058</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45930</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>46255</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46254</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>46255</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46258</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46258</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>46258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45393</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45061</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>44944</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45393</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45061</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45393</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45061</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45383</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45733</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45756</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46162</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>46106</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46121</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>44510</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>44936</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45617</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45566</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45268</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44728</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46204</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46232</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45419</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45063</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44945</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46140</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>46170</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>46185</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>46211</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>46164</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>44956</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45747</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44489</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>44577</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44577</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44669</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44720</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>44776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44860</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44874</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44721</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44785</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45541</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45406</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44956</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45730</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45679</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45159</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45401</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45226</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44816</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45737</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45265</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44894</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45063</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45105</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45054</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45406</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45632</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44529</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45321</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44901</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45678</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45054</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45225</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>45385</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44992</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45560</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45238</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45266</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45266</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45243</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45719</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44907</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44903</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45586</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45237</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45173</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45460</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45247</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45266</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45058</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45419</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45198</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>44532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44936</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45542</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45299</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45660</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45799</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45890</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45841</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45259</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45890</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45737</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44520</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45892</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45892</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>44964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45117</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45660</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45481</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45906</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45667</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45909</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44529</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45912</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45457</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45602</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44874</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>45915</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45915</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45784</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45054</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>44894</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44580</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>45272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45917</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45785</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>44903</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44917</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44522</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45771</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45748</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45691</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45919</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45790</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45754</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45429</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45268</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45740</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45583</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45925</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45925</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45926</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>44894</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45215</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45037</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44603</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45470</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45629</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45930</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45929</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45930</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45553</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45719</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45719</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45929</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45932</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45225</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45932</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44648</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45936</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45936</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45173</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45163</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45799</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44995</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45799</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45645</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45681</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45799</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45363</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45698</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45933</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45936</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45708</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45667</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45805</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45429</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45629</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45721</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45692</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45679</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45940</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45939</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45415</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45943</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45943</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>45943</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>45943</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45587</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45812</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45946</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>45811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45811</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45811</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45945</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45945</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45946</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45420</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>45945</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45816</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45392</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45295</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45815</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45815</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45816</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45816</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44862</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45816</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>45815</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45815</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45816</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45816</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45816</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45950</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45815</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45816</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45816</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45950</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45816</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45816</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45816</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45816</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45816</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45816</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45816</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45816</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45816</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45816</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45820</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45820</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45825</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45175</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45952</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45951</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>45952</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>44950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45415</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45415</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45964</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44512</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45965</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44956</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45967</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45035</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45842</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45842</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45629</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45842</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45461</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44776</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45170</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45629</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45813</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45314</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45719</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45213</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45723</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45147</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>44712</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>44722</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45816</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>44706</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45866</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45355</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45251</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45771</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45867</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45979</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45980</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45044</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45859</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45841</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45201</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45044</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45685</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46097</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45246</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44970</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45282</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45505</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>44488</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45054</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>45054</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45988</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30009,7 +30009,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44733</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>45210</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45719</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45266</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>45266</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45266</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45994</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45553</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>44903</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46122</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>45492</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45995</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46128</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45561</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45419</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46003</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46003</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46003</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>46134</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46134</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>46003</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>46003</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46003</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>46003</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>46135</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>46135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>46009</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>46009</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>46009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>46003</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>45706</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>44964</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>46052</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45917</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>46021</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45446</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>46021</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44901</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44903</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>45617</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46030</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45665</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46030</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46029</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46029</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46031</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46031</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>45712</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>46035</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>46003</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46035</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>44756</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45708</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46035</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45112</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46041</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>46041</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45881</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45641</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45145</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35662,7 +35662,7 @@
         <v>46003</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45266</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>45246</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35881,7 +35881,7 @@
         <v>45175</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46055</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46056</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>46056</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45364</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>46142</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45641</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>46146</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>46081</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46154</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45985</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46073</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46077</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>46154</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>46083</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>46009</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45986</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46003</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>46003</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>46090</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>46090</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45204</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>46091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>44970</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>46091</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>46160</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>46091</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46093</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>46160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>46094</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45622</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46163</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45700</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45986</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45639</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>46167</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46167</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46168</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>46168</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>46171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>46175</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>46175</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46175</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>46178</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46191</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46195</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>46197</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>46204</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>46204</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>46204</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45510</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>46221</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46267</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>46267</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>46267</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46225</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46267</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>46272</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46269</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>46274</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46274</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46233</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46275</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46275</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>46275</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>46233</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46275</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>46280</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46279</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>46234</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46282</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46238</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>46238</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46282</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>46286</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>46286</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46286</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46286</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>46029</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>46288</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>46288</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46286</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46290</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46009</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46246</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46289</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46246</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46289</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>46290</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>46252</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>46294</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46248</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46252</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46246</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>46252</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46252</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45005</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46296</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>46254</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46254</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46255</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>46058</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45930</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>46255</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46254</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>46255</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46258</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46258</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>46258</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>44678</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45393</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45061</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>44944</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45393</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45061</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45393</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45061</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45383</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45733</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45756</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45775</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45775</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>46162</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46190</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44510</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>46121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46311</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44936</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45566</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>46204</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>46232</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44944</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>44791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46140</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>46164</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46211</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45419</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>46310</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>44956</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44860</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>44577</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44880</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>45229</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45537</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>45266</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44648</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45585</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45117</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45295</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45712</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44970</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44970</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45771</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>45586</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45541</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45712</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45406</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45225</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45190</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45415</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44580</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45708</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45259</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45321</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45667</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44529</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45079</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45667</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45355</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45553</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45201</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45446</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45660</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45841</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45737</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45890</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45890</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45892</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45892</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45226</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45835</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45401</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>46070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46003</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45708</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45993</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45665</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46003</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45638</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44756</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45906</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45881</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45881</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>46142</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45915</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45641</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>45912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45916</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45266</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45925</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45925</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45054</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45926</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45933</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45406</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45938</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45943</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45940</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45385</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45945</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45945</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45691</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46009</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45950</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45986</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46003</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45950</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45952</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46154</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>46154</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46155</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>46154</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46081</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44970</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44706</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46160</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45740</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46161</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45246</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45971</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45582</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45971</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>46163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45251</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45457</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44581</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45754</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>44903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45979</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45980</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45981</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45981</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45639</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46167</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45985</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45641</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45700</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45213</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45622</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45299</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45730</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>46167</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45993</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45314</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46168</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45308</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45995</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45492</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45560</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45112</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45698</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45723</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>46001</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45719</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45719</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45629</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46003</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46003</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46003</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46003</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>46171</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>46003</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46009</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46003</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>46013</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46013</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44520</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>46021</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>46021</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45602</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>46175</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>46029</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>46029</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45617</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>46030</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>46031</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>46031</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>46031</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46035</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46175</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46035</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>46035</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>46175</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46041</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46041</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46178</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44970</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45420</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45678</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46055</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45204</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>46056</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>46056</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>45364</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45054</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44488</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44956</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44903</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45698</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45210</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>46077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45561</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45063</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45583</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46083</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45542</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>46085</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45282</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>46090</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45295</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46091</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45629</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46195</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46191</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>46091</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46094</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46093</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44894</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46195</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46104</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46106</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>46106</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46195</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46197</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45009</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45553</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>45660</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>46122</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>44522</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>46199</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>46199</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45266</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45266</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45173</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46199</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46128</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45679</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46203</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44956</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45470</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46135</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45415</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45415</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>46134</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>44894</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>46204</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46204</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44901</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45505</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45510</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45054</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45392</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45044</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46221</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44712</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46225</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45737</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46272</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>46274</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>46233</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45215</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46274</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>46275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>46275</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46275</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46275</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46233</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45044</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46234</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46279</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46279</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45481</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>44974</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44974</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46238</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45170</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46238</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46238</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46238</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45049</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46282</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>46282</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44964</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>46029</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44532</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44980</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44903</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45266</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46286</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>46286</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>46286</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44862</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45700</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>46289</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>46246</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45573</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>46289</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45393</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46246</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44995</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>46248</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45237</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46009</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45419</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45629</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45679</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45429</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>46290</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>44603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46252</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46252</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45261</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>46252</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>46294</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46252</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>44894</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45163</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45930</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>46058</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45005</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45266</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45266</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45112</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>46296</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>46254</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46255</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>46254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46254</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46092</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45198</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>44722</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45054</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45035</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45685</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44924</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46258</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45036</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>46258</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45777</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45785</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45784</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45405</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45429</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45748</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>45268</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44917</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45790</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45363</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45645</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45799</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45799</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45799</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>45799</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45681</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45805</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45811</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45811</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45811</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45692</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45721</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45321</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>46310</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46310</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>46310</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>46269</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45812</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45816</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45816</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45816</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45816</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>45815</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45815</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45816</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45816</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>45816</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45816</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45816</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45816</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45816</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45816</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45816</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45816</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45816</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45816</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45816</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45815</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45816</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45816</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45816</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45815</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45816</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45815</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>46267</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45820</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45820</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>46267</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45825</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45827</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>46310</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45841</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45813</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45842</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>44776</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45842</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45842</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45851</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45866</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45867</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45841</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>44678</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45393</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45061</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>44944</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45393</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45061</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45393</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45061</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45383</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45733</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45747</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45747</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45756</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45775</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45775</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46162</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>46190</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>46190</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44510</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>46121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46311</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44936</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46231</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45566</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>44728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>46204</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>46232</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44944</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>44791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46140</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46185</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>46164</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46211</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45063</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45419</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>46310</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>44956</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45747</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44860</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44489</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>44577</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>44720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44880</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>45229</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45537</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>45266</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44648</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45585</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45117</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45295</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44894</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45712</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44970</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44970</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45771</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>45586</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45541</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>45712</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45406</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45225</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45719</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45190</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45415</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44580</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45708</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45259</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45321</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45667</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44529</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45079</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45667</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45355</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45553</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45201</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45446</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45660</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45841</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45737</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45799</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45890</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45890</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45892</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45892</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45226</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45835</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45401</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>46070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46003</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45708</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45993</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45665</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46003</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44903</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45638</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44756</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45906</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>45881</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45881</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>46142</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45915</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45641</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>45912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45916</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46146</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44924</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45266</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46146</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45925</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45925</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45054</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45926</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45930</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45932</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45932</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45933</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45406</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45938</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45943</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45940</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45385</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45945</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45945</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45945</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45946</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45946</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45946</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45691</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46009</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45950</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45986</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46003</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45950</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45950</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45952</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>46154</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>46154</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45952</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46155</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>46154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>46154</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>46081</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44970</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44706</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46160</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45740</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46161</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45246</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45964</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45971</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45582</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45971</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>46163</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45251</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45457</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44950</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44581</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45754</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44907</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>44903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45419</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45979</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45980</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45981</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>45981</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45639</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46167</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45985</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45641</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45700</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45213</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45988</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45622</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45299</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45730</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45988</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>46167</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45993</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45314</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46168</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45308</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45995</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45492</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45560</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45112</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45698</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45723</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>46001</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45719</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45719</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45629</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>46003</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46003</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46003</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>46003</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>46171</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>46003</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46009</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46009</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>46009</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46003</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>46009</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>46013</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46013</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44520</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>46021</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>46021</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45602</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>46175</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>46029</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>46029</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45617</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>46030</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>46031</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>46031</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>46031</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46035</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46175</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46035</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>46035</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>46175</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>46175</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46041</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46041</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46178</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44970</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45420</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45678</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46055</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45204</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45272</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>46056</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>46056</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>45364</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45054</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>44488</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44956</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44903</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45698</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>46073</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>45210</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>46077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45561</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45063</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45583</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46083</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45542</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>46085</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45282</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>46090</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45295</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46091</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45629</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46195</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46191</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>46091</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>46094</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46093</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46097</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44894</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46195</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46104</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46106</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>46106</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46195</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46197</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45009</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45553</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>45660</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>46122</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>44522</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>46199</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>46199</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45266</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45266</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45173</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46199</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46128</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45679</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46203</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44956</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45470</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46135</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46135</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45415</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45415</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>46134</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>44894</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>46204</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46204</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>44901</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45505</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45510</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45054</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45054</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45392</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45044</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46221</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44712</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46225</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45737</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46272</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>46274</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>46233</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45215</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46274</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>46275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>46275</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46275</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46275</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46233</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45044</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46234</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46279</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46279</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45481</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>44974</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44974</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46238</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45170</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46238</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46238</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46238</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45049</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46282</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>44992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>46282</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44964</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>46029</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>44532</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44980</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44903</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45266</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>46286</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>46286</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>46286</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44862</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45700</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>46289</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>46246</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>45573</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>46289</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45393</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45247</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46246</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44995</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>46248</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>45237</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46009</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45419</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45629</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45679</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45429</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>46290</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>44603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46252</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>46252</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45261</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>46252</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>46294</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>46252</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>44894</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45163</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45930</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>46058</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45005</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45266</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45266</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45112</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>46296</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>46254</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>46255</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>46254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>46254</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46092</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45198</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>44722</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45054</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45035</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45685</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44924</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46258</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45036</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>46258</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45777</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46255</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45785</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45784</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45405</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45429</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45748</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>45268</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44917</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45790</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45363</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45645</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45799</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45799</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41227,7 +41227,7 @@
         <v>45799</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>45799</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45681</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45805</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45811</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45811</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45811</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45692</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45721</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45321</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>46310</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46310</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>46310</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>46269</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45812</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45816</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45816</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45816</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45816</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>45815</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45815</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45816</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45816</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>45816</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>45816</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45816</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45816</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45816</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45816</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45816</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45816</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45816</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45816</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45816</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45815</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45816</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45816</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45816</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45815</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45816</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45815</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>46267</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45820</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45820</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>46267</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45825</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45827</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>46310</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45841</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45813</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45842</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>44776</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45842</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45842</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45851</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45866</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45867</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45841</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>44678</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45393</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45061</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>44944</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45393</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45061</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45393</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45061</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45383</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45733</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45747</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45747</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45756</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45775</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45775</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46162</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>46190</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>46190</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44510</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>46121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46311</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44936</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45617</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45566</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45791</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>44728</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44944</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>44791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46164</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45419</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45364</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>46310</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45063</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44956</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44860</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44577</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44880</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>45660</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45036</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45259</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45737</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>45892</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44964</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45904</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45904</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45406</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44901</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45906</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>46160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>46161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45622</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>46163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45894</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45639</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45919</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45925</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>46168</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45259</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45641</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>46168</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45930</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45932</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>45932</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45266</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45933</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45936</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45246</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45938</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45940</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>46175</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45939</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44956</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45943</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45679</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45159</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45943</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45943</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45226</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45253</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45393</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45946</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45945</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44529</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45945</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45931</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45950</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45950</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44894</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45950</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45952</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44898</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45632</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45582</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45054</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45712</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46191</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45225</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45385</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45967</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>46195</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45971</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45971</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46197</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45700</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45971</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45719</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44981</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46199</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46199</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45063</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45816</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45237</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45173</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46199</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45058</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45238</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45542</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46204</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>46204</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45981</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45981</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45243</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46204</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44907</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46204</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45510</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45985</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45985</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44970</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>44964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45638</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45660</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45993</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45993</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45995</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45667</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46221</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>46001</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45777</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>46003</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46003</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46003</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46225</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46003</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>46003</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45784</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>46003</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>46233</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>46233</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45405</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46009</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>46009</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>46279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>46009</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>46009</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>46003</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46279</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46013</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46013</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45748</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46279</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46234</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45790</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46021</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>46021</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45429</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>46238</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45268</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45617</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46282</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46238</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46030</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46282</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46030</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46029</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46029</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45266</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46031</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46031</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46031</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46286</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>46286</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46035</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45419</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46035</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46035</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46041</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46029</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46288</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45173</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45799</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45645</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45799</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45799</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46286</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45363</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46246</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>46289</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45805</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46289</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>46056</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46056</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45721</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45321</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>46290</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45692</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>46252</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45812</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45811</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>46294</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45816</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45815</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45815</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45816</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45816</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45816</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45815</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45815</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45816</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45816</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45816</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45299</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46252</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>46246</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45815</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45816</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46252</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45816</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45816</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45816</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45816</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45816</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45816</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45816</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45816</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45816</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45816</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45816</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45816</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>46252</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45820</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45820</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>46073</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46077</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45825</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>46083</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45827</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46254</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45832</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>46085</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>46090</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46090</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46091</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45835</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46058</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>46091</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45930</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>46093</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46092</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46094</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45841</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45842</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45842</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45842</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44776</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44520</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>46254</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45813</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>46104</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46258</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>46106</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45851</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46106</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>46258</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45481</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45867</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>46122</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45859</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46134</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46134</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44529</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44874</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45054</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44924</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44894</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>44894</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>46310</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46310</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>46135</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45272</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>46310</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>46135</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>46310</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>44903</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>46267</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45706</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46052</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45446</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45771</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45691</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46267</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>46312</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46312</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46312</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44903</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45665</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44581</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45740</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45583</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46269</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44894</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>45037</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44603</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46003</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46070</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46310</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46314</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44756</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45708</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45881</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45553</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45881</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46274</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46003</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45225</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>46318</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46318</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>46318</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46317</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>46318</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46142</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45698</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46146</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45708</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45641</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>46146</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45259</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45429</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>46081</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>46154</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45985</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45112</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45415</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46154</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46009</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45587</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45420</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46155</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45295</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>46003</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>46003</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45204</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44512</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45009</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>44974</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>44956</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45035</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45629</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45461</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45629</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45204</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45719</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45723</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45147</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44712</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>45063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45190</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45201</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45044</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45685</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45054</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45054</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45266</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45266</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44733</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45210</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45719</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45541</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45737</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45063</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45054</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45406</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45229</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45321</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>44901</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44992</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45266</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45266</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45198</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44532</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>44936</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45573</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45457</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45602</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44580</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44522</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45170</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45754</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45585</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45215</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45470</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45629</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45191</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>45719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45719</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44648</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45163</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>44995</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45667</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45629</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45679</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45392</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44862</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45175</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45415</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45415</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44749</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45261</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45170</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45314</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45213</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44722</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>44706</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45355</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45251</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>45771</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45044</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44970</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>44970</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>44974</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45282</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45505</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>44964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>45266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45553</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>44903</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45492</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45561</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45419</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>44678</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45393</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45061</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44944</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45393</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45061</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45393</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45061</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45383</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45733</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45747</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45747</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45756</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45775</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>46162</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>

--- a/Översikt KALIX.xlsx
+++ b/Översikt KALIX.xlsx
@@ -601,7 +601,7 @@
         <v>46030</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>46238</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>44530</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>45188</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>46121</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>44510</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>46106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>46121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46311</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>44936</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>46231</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45617</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45566</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45268</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>46204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45791</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>44728</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44944</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>44791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>46170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>46211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46164</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45419</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45364</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46252</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>46310</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45063</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44956</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44860</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44497</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44577</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44577</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44669</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44720</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44880</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>44785</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>44721</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>45660</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45890</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45266</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45036</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45259</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>45890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45737</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>45892</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>45892</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44964</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45904</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45904</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45406</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44901</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45906</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46160</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>46160</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>46161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>45915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>45622</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>46163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45894</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45986</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45639</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45919</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45925</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>46168</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45259</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45641</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>46168</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45930</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45932</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>45932</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45266</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45936</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46175</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45933</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45936</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45246</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>45938</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45940</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>46175</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45939</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44956</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45943</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45679</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45159</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45943</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45943</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45226</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45253</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45393</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45946</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45946</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45945</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45945</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44529</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44894</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45945</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45931</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45950</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45950</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45950</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44894</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45950</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46178</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45952</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44898</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45632</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45582</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45054</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45712</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46191</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45225</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45385</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45967</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>46195</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45971</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>46195</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45971</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>46197</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45700</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45971</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45719</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44981</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46199</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46199</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45063</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45816</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45237</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45173</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46199</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45058</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45238</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45542</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46204</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>46204</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45981</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45981</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45243</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46204</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44907</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46204</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45510</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45985</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45985</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44970</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>44964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45638</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45660</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45993</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45994</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45993</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45995</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45667</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46221</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>46001</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45777</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>46003</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46003</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>46003</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>46225</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>46003</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>46003</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45784</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>46003</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>46233</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>46233</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45405</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>46280</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>46009</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>46009</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>46279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>46009</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>46009</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>46003</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>46279</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46013</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46013</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45748</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45917</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>46279</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46234</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45790</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46021</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>46021</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>45429</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>46238</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45268</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45617</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46282</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46238</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46030</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46282</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>46030</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46029</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46029</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45266</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46031</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46031</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46031</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>46286</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>46286</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46035</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45419</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46035</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>46035</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>46041</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46029</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46041</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46288</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45173</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45799</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45645</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45681</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45799</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45799</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46286</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45363</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46246</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>46289</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>45805</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>46246</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>46289</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>46056</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>46056</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45721</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45321</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>46290</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45692</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>46252</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45812</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45811</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45811</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>46294</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45816</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45815</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45815</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45816</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45816</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45816</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45815</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45815</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45816</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45816</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45816</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45299</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>46252</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>46246</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45815</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45816</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46252</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45816</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45816</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45816</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45816</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45816</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45816</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45816</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45816</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45816</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45816</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45816</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45816</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>46252</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45820</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45820</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>46073</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45005</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>46077</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>46296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45825</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>46083</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45827</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46254</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45831</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45832</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>46085</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>46254</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>46090</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46090</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46091</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46255</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46091</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45835</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46058</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>46091</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45930</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>46093</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46092</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46094</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45841</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45842</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45842</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45842</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44776</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44520</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>46254</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45813</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>46104</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46258</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>46106</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45851</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>46106</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>46106</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>46258</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45481</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45867</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>46122</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45859</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45841</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46134</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>46134</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44529</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44874</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45054</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44924</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44894</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>44894</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>46310</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46310</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>46135</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45272</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>46310</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>46135</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>46310</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>44903</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>46267</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45706</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46052</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45446</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>45771</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45691</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46267</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>46312</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46312</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46312</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44903</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45665</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44581</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45740</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45583</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>46269</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44894</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>45037</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44603</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46003</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>46070</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46310</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46314</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44756</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45708</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45881</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45553</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45881</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46274</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46003</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45225</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>46318</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46318</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>46318</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46317</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>46318</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>46274</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46142</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45698</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46146</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45708</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45641</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46275</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>46275</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>46146</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45259</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45429</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>46081</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>46154</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45985</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45112</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45415</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>46154</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46009</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46154</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46154</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>45587</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45986</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>45420</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46155</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45295</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>46003</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>46003</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45204</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>45308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>44512</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45009</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>44974</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>44956</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45035</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45629</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45461</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45629</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45204</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45719</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45723</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45147</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44712</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>45063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45190</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45201</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45044</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45685</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45246</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45054</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45054</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45266</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45266</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44733</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45210</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45719</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45541</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45737</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45063</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45054</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45406</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45229</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45321</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>44901</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44992</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45266</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45266</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45247</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45198</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44532</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>44936</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45573</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45457</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45602</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44580</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44522</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45170</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45754</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45585</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45215</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45470</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45629</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45191</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>45719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45719</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44648</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45163</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>44995</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45667</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45629</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45679</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45392</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44862</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45175</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45415</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45415</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44749</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45261</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45170</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45314</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45213</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44722</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>44706</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45355</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45251</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>45771</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45044</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44970</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>44970</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>44974</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45282</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45505</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>44964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45991,7 +45991,7 @@
         <v>45266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45266</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45553</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>44903</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45492</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45561</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45419</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>44678</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45393</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45061</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>44944</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45393</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45061</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45393</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45061</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45383</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45733</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45747</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45747</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45756</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45775</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45775</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>46162</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
